--- a/reports/member_funnel/downloads/member_funnel_1d_target_vip.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_vip.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>veritaskm</t>
+          <t>kk_2905067716</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01084555847</t>
+          <t>01099172715</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EDM_0220</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudan Pro 3L Shell</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_2905067716</t>
+          <t>kk_4201213646</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01099172715</t>
+          <t>01027969918</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_ECOM_cart_sale</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paracutie II Windbreaker</t>
+          <t>Cove Beach Pant</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
